--- a/docs/MODEL_SPREADSHEET.xlsx
+++ b/docs/MODEL_SPREADSHEET.xlsx
@@ -719,7 +719,7 @@
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>BCSC v3 (Breast Cancer Surveillance Consortium 5- and 10-year risk)
-[code and data retrieved (public download, no password needed), awaiting a licence determination] 
+[code and data retrieved (public download, no password needed), awaiting a licence determination]
 Interim: BCRAT / Gail model (absolute invasive breast cancer risk) (1989)</t>
         </is>
       </c>
@@ -846,7 +846,7 @@
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>BCSC v2.0 (Tice 2015, adds benign breast disease and a ten-year horizon)
-[source gated behind a download-request form; article not open access] 
+[source gated behind a download-request form; article not open access]
 Interim: BCSC breast density model (Tice 2008, the BCSC calculator's version 1.0, 5-year risk) (2008)</t>
         </is>
       </c>
@@ -1675,7 +1675,7 @@
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Interpretable LR model for stroke in newly diagnosed atrial fibrillation
-[one missing constant] 
+[one missing constant]
 Interim: CHA2DS2-VASc (stroke risk in atrial fibrillation) (2010)</t>
         </is>
       </c>
@@ -3843,7 +3843,7 @@
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>ITA.LI.CA integrated prognostic score (HCC survival)
-[inputs the platform does not hold] 
+[inputs the platform does not hold]
 Interim: ALBI grade (albumin-bilirubin liver function) (2015)</t>
         </is>
       </c>
@@ -5788,11 +5788,11 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>BCSC v3 (Breast Cancer Surveillance Consortium 5- and 10-year risk)
-[code and data retrieved (public download, no password needed), awaiting a licence determination] 
+[code and data retrieved (public download, no password needed), awaiting a licence determination]
 Interim: BCRAT / Gail model (absolute invasive breast cancer risk) (1989)
 [verified]
 BCSC v2.0 (Tice 2015, adds benign breast disease and a ten-year horizon)
-[source gated behind a download-request form; article not open access] 
+[source gated behind a download-request form; article not open access]
 Interim: BCSC breast density model (Tice 2008, the BCSC calculator's version 1.0, 5-year risk) (2008)
 [NOT verified]</t>
         </is>
@@ -5835,7 +5835,7 @@
           <t>GRACE 2003 in-hospital mortality score (acute coronary syndromes)
 [verified]
 Interpretable LR model for stroke in newly diagnosed atrial fibrillation
-[one missing constant] 
+[one missing constant]
 Interim: CHA2DS2-VASc (stroke risk in atrial fibrillation) (2010)
 [verified]
 ATRIA stroke risk score (atrial fibrillation)
@@ -5988,7 +5988,7 @@
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t>ITA.LI.CA integrated prognostic score (HCC survival)
-[inputs the platform does not hold] 
+[inputs the platform does not hold]
 Interim: ALBI grade (albumin-bilirubin liver function) (2015)
 [verified]</t>
         </is>
